--- a/示其的逆袭计划/Office学习/day2 (2026.8.9)/Excel第2课_练习.xlsx
+++ b/示其的逆袭计划/Office学习/day2 (2026.8.9)/Excel第2课_练习.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="190" yWindow="560" windowWidth="18910" windowHeight="7200" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="练习说明" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,28 +19,54 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <i val="1"/>
-      <color rgb="00808080"/>
+      <color rgb="FF808080"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <sz val="9"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="4">
@@ -53,12 +78,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004F81BD"/>
+        <fgColor rgb="FF4F81BD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,23 +97,24 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -101,9 +127,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="20" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -467,13 +498,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="17.5" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Excel 第 2 课练习（2026.8.9）</t>
@@ -616,19 +647,16 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="3" max="5"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="12" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -657,14 +685,14 @@
           <t>英语</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>复制区域（Ctrl+C / Ctrl+V）</t>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
+          <t>学号</t>
         </is>
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
-          <t>复制区域</t>
+          <t>姓名</t>
         </is>
       </c>
       <c r="J1" s="4" t="inlineStr">
@@ -710,12 +738,29 @@
       <c r="E2" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="G2" s="7" t="n"/>
-      <c r="H2" s="7" t="n"/>
-      <c r="J2" s="7" t="n"/>
-      <c r="K2" s="7" t="n"/>
-      <c r="L2" s="7" t="n"/>
-      <c r="M2" s="7" t="n"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>001</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="J2" s="7">
+        <f>SUM(D2:D11)</f>
+        <v/>
+      </c>
+      <c r="K2" s="9" t="n">
+        <v>46243</v>
+      </c>
+      <c r="L2" s="10" t="n">
+        <v>0.8701388888888889</v>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -739,9 +784,19 @@
       <c r="E3" s="6" t="n">
         <v>92</v>
       </c>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="7" t="n"/>
-      <c r="M3" s="7" t="n"/>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>002</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -765,9 +820,19 @@
       <c r="E4" s="6" t="n">
         <v>74</v>
       </c>
-      <c r="G4" s="7" t="n"/>
-      <c r="H4" s="7" t="n"/>
-      <c r="M4" s="7" t="n"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>003</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -791,9 +856,19 @@
       <c r="E5" s="6" t="n">
         <v>63</v>
       </c>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="7" t="n"/>
-      <c r="M5" s="7" t="n"/>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>004</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -817,9 +892,19 @@
       <c r="E6" s="6" t="n">
         <v>85</v>
       </c>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>005</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>孙七</t>
+        </is>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -843,8 +928,16 @@
       <c r="E7" s="6" t="n">
         <v>90</v>
       </c>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>周八</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -868,8 +961,16 @@
       <c r="E8" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="G8" s="7" t="n"/>
-      <c r="H8" s="7" t="n"/>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>007</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>吴九</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -893,8 +994,16 @@
       <c r="E9" s="6" t="n">
         <v>55</v>
       </c>
-      <c r="G9" s="7" t="n"/>
-      <c r="H9" s="7" t="n"/>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>008</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>郑十</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -918,8 +1027,16 @@
       <c r="E10" s="6" t="n">
         <v>95</v>
       </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="7" t="n"/>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>009</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>钱一</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -943,8 +1060,20 @@
       <c r="E11" s="6" t="n">
         <v>71</v>
       </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>010</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>陈二</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="G12" s="5" t="n"/>
+      <c r="H12" s="5" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -955,6 +1084,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -965,14 +1095,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="1" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1001,51 +1126,126 @@
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="n"/>
-      <c r="C2" s="7" t="n"/>
-      <c r="D2" s="7" t="n"/>
-      <c r="E2" s="7" t="n"/>
-      <c r="F2" s="7" t="n"/>
+      <c r="B2" s="7">
+        <f>$A2*B$1</f>
+        <v/>
+      </c>
+      <c r="C2" s="7">
+        <f>$A2*C$1</f>
+        <v/>
+      </c>
+      <c r="D2" s="7">
+        <f>$A2*D$1</f>
+        <v/>
+      </c>
+      <c r="E2" s="7">
+        <f>$A2*E$1</f>
+        <v/>
+      </c>
+      <c r="F2" s="7">
+        <f>$A2*F$1</f>
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="n"/>
-      <c r="C3" s="7" t="n"/>
-      <c r="D3" s="7" t="n"/>
-      <c r="E3" s="7" t="n"/>
-      <c r="F3" s="7" t="n"/>
+      <c r="B3" s="7">
+        <f>$A3*B$1</f>
+        <v/>
+      </c>
+      <c r="C3" s="7">
+        <f>$A3*C$1</f>
+        <v/>
+      </c>
+      <c r="D3" s="7">
+        <f>$A3*D$1</f>
+        <v/>
+      </c>
+      <c r="E3" s="7">
+        <f>$A3*E$1</f>
+        <v/>
+      </c>
+      <c r="F3" s="7">
+        <f>$A3*F$1</f>
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="n"/>
-      <c r="C4" s="7" t="n"/>
-      <c r="D4" s="7" t="n"/>
-      <c r="E4" s="7" t="n"/>
-      <c r="F4" s="7" t="n"/>
+      <c r="B4" s="7">
+        <f>$A4*B$1</f>
+        <v/>
+      </c>
+      <c r="C4" s="7">
+        <f>$A4*C$1</f>
+        <v/>
+      </c>
+      <c r="D4" s="7">
+        <f>$A4*D$1</f>
+        <v/>
+      </c>
+      <c r="E4" s="7">
+        <f>$A4*E$1</f>
+        <v/>
+      </c>
+      <c r="F4" s="7">
+        <f>$A4*F$1</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
-      <c r="F5" s="7" t="n"/>
+      <c r="B5" s="7">
+        <f>$A5*B$1</f>
+        <v/>
+      </c>
+      <c r="C5" s="7">
+        <f>$A5*C$1</f>
+        <v/>
+      </c>
+      <c r="D5" s="7">
+        <f>$A5*D$1</f>
+        <v/>
+      </c>
+      <c r="E5" s="7">
+        <f>$A5*E$1</f>
+        <v/>
+      </c>
+      <c r="F5" s="7">
+        <f>$A5*F$1</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
+      <c r="B6" s="7">
+        <f>$A6*B$1</f>
+        <v/>
+      </c>
+      <c r="C6" s="7">
+        <f>$A6*C$1</f>
+        <v/>
+      </c>
+      <c r="D6" s="7">
+        <f>$A6*D$1</f>
+        <v/>
+      </c>
+      <c r="E6" s="7">
+        <f>$A6*E$1</f>
+        <v/>
+      </c>
+      <c r="F6" s="7">
+        <f>$A6*F$1</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1073,13 +1273,11 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="3" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1158,12 +1356,12 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>003</t>
+          <t>005</t>
         </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>王五</t>
+          <t>孙七</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
@@ -1172,10 +1370,10 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5">
@@ -1204,12 +1402,12 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>005</t>
+          <t>003</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>孙七</t>
+          <t>王五</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
@@ -1218,10 +1416,10 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
